--- a/output/yearly_population_iteration_33_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_33_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9063</v>
+        <v>6047</v>
       </c>
       <c r="C2" t="n">
-        <v>3581</v>
+        <v>11316</v>
       </c>
       <c r="D2" t="n">
-        <v>31551</v>
+        <v>26050</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5268</v>
+        <v>3963</v>
       </c>
       <c r="C3" t="n">
-        <v>3129</v>
+        <v>5664</v>
       </c>
       <c r="D3" t="n">
-        <v>18228</v>
+        <v>11128</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3663</v>
+        <v>3338</v>
       </c>
       <c r="C4" t="n">
-        <v>4172</v>
+        <v>5966</v>
       </c>
       <c r="D4" t="n">
-        <v>8582</v>
+        <v>5819</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2197</v>
+        <v>2232</v>
       </c>
       <c r="C5" t="n">
-        <v>3474</v>
+        <v>4742</v>
       </c>
       <c r="D5" t="n">
-        <v>3060</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1298</v>
+        <v>1225</v>
       </c>
       <c r="C6" t="n">
-        <v>2450</v>
+        <v>2718</v>
       </c>
       <c r="D6" t="n">
-        <v>1197</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>642</v>
+        <v>535</v>
       </c>
       <c r="C7" t="n">
-        <v>1670</v>
+        <v>1346</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="C8" t="n">
-        <v>875</v>
+        <v>596</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>392</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10192</v>
+        <v>8316</v>
       </c>
       <c r="C2" t="n">
-        <v>10480</v>
+        <v>9277</v>
       </c>
       <c r="D2" t="n">
-        <v>28434</v>
+        <v>25210</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5620</v>
+        <v>4038</v>
       </c>
       <c r="C3" t="n">
-        <v>2935</v>
+        <v>7281</v>
       </c>
       <c r="D3" t="n">
-        <v>18815</v>
+        <v>12409</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3712</v>
+        <v>3096</v>
       </c>
       <c r="C4" t="n">
-        <v>3554</v>
+        <v>5636</v>
       </c>
       <c r="D4" t="n">
-        <v>9895</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2486</v>
+        <v>2403</v>
       </c>
       <c r="C5" t="n">
-        <v>3723</v>
+        <v>5230</v>
       </c>
       <c r="D5" t="n">
-        <v>3785</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1547</v>
+        <v>1515</v>
       </c>
       <c r="C6" t="n">
-        <v>2854</v>
+        <v>3623</v>
       </c>
       <c r="D6" t="n">
-        <v>1467</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>823</v>
+        <v>752</v>
       </c>
       <c r="C7" t="n">
-        <v>1996</v>
+        <v>1950</v>
       </c>
       <c r="D7" t="n">
-        <v>728</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>355</v>
+        <v>298</v>
       </c>
       <c r="C8" t="n">
-        <v>1217</v>
+        <v>926</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>586</v>
+        <v>408</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>250</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11321</v>
+        <v>9259</v>
       </c>
       <c r="C2" t="n">
-        <v>13398</v>
+        <v>12509</v>
       </c>
       <c r="D2" t="n">
-        <v>29942</v>
+        <v>25541</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6067</v>
+        <v>4693</v>
       </c>
       <c r="C3" t="n">
-        <v>5322</v>
+        <v>7192</v>
       </c>
       <c r="D3" t="n">
-        <v>18765</v>
+        <v>13233</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3811</v>
+        <v>2977</v>
       </c>
       <c r="C4" t="n">
-        <v>3178</v>
+        <v>6260</v>
       </c>
       <c r="D4" t="n">
-        <v>10783</v>
+        <v>7170</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2663</v>
+        <v>2423</v>
       </c>
       <c r="C5" t="n">
-        <v>3538</v>
+        <v>5246</v>
       </c>
       <c r="D5" t="n">
-        <v>4549</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1747</v>
+        <v>1709</v>
       </c>
       <c r="C6" t="n">
-        <v>3187</v>
+        <v>4268</v>
       </c>
       <c r="D6" t="n">
-        <v>1745</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>995</v>
+        <v>948</v>
       </c>
       <c r="C7" t="n">
-        <v>2320</v>
+        <v>2618</v>
       </c>
       <c r="D7" t="n">
-        <v>814</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>474</v>
+        <v>420</v>
       </c>
       <c r="C8" t="n">
-        <v>1509</v>
+        <v>1327</v>
       </c>
       <c r="D8" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="C9" t="n">
-        <v>826</v>
+        <v>610</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>392</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10413</v>
+        <v>8418</v>
       </c>
       <c r="C2" t="n">
-        <v>9110</v>
+        <v>8406</v>
       </c>
       <c r="D2" t="n">
-        <v>24674</v>
+        <v>20940</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7072</v>
+        <v>5535</v>
       </c>
       <c r="C3" t="n">
-        <v>8028</v>
+        <v>11029</v>
       </c>
       <c r="D3" t="n">
-        <v>20606</v>
+        <v>14329</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2460</v>
+        <v>2238</v>
       </c>
       <c r="C4" t="n">
-        <v>5135</v>
+        <v>8521</v>
       </c>
       <c r="D4" t="n">
-        <v>10183</v>
+        <v>6971</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1614</v>
+        <v>1579</v>
       </c>
       <c r="C5" t="n">
-        <v>3123</v>
+        <v>4182</v>
       </c>
       <c r="D5" t="n">
-        <v>2932</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>919</v>
+        <v>875</v>
       </c>
       <c r="C6" t="n">
-        <v>2273</v>
+        <v>2565</v>
       </c>
       <c r="D6" t="n">
-        <v>797</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>437</v>
+        <v>388</v>
       </c>
       <c r="C7" t="n">
-        <v>1478</v>
+        <v>1300</v>
       </c>
       <c r="D7" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C8" t="n">
-        <v>809</v>
+        <v>597</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>384</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6355</v>
+        <v>5052</v>
       </c>
       <c r="C2" t="n">
-        <v>4344</v>
+        <v>4477</v>
       </c>
       <c r="D2" t="n">
-        <v>17075</v>
+        <v>15797</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7308</v>
+        <v>5826</v>
       </c>
       <c r="C3" t="n">
-        <v>7724</v>
+        <v>8896</v>
       </c>
       <c r="D3" t="n">
-        <v>19972</v>
+        <v>14402</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3620</v>
+        <v>3061</v>
       </c>
       <c r="C4" t="n">
-        <v>6509</v>
+        <v>9768</v>
       </c>
       <c r="D4" t="n">
-        <v>11669</v>
+        <v>8023</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1821</v>
+        <v>1750</v>
       </c>
       <c r="C5" t="n">
-        <v>4038</v>
+        <v>6128</v>
       </c>
       <c r="D5" t="n">
-        <v>3804</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1087</v>
+        <v>1052</v>
       </c>
       <c r="C6" t="n">
-        <v>2683</v>
+        <v>3295</v>
       </c>
       <c r="D6" t="n">
-        <v>1015</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>412</v>
+        <v>363</v>
       </c>
       <c r="C7" t="n">
-        <v>1825</v>
+        <v>1748</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>1041</v>
+        <v>810</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>432</v>
+        <v>338</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7048</v>
+        <v>6314</v>
       </c>
       <c r="C2" t="n">
-        <v>9268</v>
+        <v>6252</v>
       </c>
       <c r="D2" t="n">
-        <v>20818</v>
+        <v>17545</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5797</v>
+        <v>4616</v>
       </c>
       <c r="C3" t="n">
-        <v>5440</v>
+        <v>5997</v>
       </c>
       <c r="D3" t="n">
-        <v>18372</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4496</v>
+        <v>3675</v>
       </c>
       <c r="C4" t="n">
-        <v>6968</v>
+        <v>9129</v>
       </c>
       <c r="D4" t="n">
-        <v>12669</v>
+        <v>8743</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2279</v>
+        <v>2051</v>
       </c>
       <c r="C5" t="n">
-        <v>5116</v>
+        <v>7806</v>
       </c>
       <c r="D5" t="n">
-        <v>4896</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1278</v>
+        <v>1233</v>
       </c>
       <c r="C6" t="n">
-        <v>3294</v>
+        <v>4540</v>
       </c>
       <c r="D6" t="n">
-        <v>1403</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>601</v>
+        <v>558</v>
       </c>
       <c r="C7" t="n">
-        <v>2212</v>
+        <v>2446</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="C8" t="n">
-        <v>1365</v>
+        <v>1203</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>662</v>
+        <v>521</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2467,7 +2467,7 @@
         <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2579,7 +2579,7 @@
         <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4205</v>
+        <v>3743</v>
       </c>
       <c r="C2" t="n">
-        <v>4308</v>
+        <v>2906</v>
       </c>
       <c r="D2" t="n">
-        <v>14508</v>
+        <v>12093</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5882</v>
+        <v>4847</v>
       </c>
       <c r="C3" t="n">
-        <v>6560</v>
+        <v>5892</v>
       </c>
       <c r="D3" t="n">
-        <v>18214</v>
+        <v>13977</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4943</v>
+        <v>4060</v>
       </c>
       <c r="C4" t="n">
-        <v>6993</v>
+        <v>8850</v>
       </c>
       <c r="D4" t="n">
-        <v>13431</v>
+        <v>9364</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2345</v>
+        <v>2154</v>
       </c>
       <c r="C5" t="n">
-        <v>6249</v>
+        <v>9194</v>
       </c>
       <c r="D5" t="n">
-        <v>5169</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1074</v>
+        <v>1016</v>
       </c>
       <c r="C6" t="n">
-        <v>4055</v>
+        <v>5443</v>
       </c>
       <c r="D6" t="n">
-        <v>1367</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="C7" t="n">
-        <v>2397</v>
+        <v>2431</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1063</v>
+        <v>887</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2764,7 +2764,7 @@
         <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2876,7 +2876,7 @@
         <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4995</v>
+        <v>4268</v>
       </c>
       <c r="C2" t="n">
-        <v>5194</v>
+        <v>6278</v>
       </c>
       <c r="D2" t="n">
-        <v>15713</v>
+        <v>10837</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4436</v>
+        <v>3746</v>
       </c>
       <c r="C3" t="n">
-        <v>4934</v>
+        <v>3990</v>
       </c>
       <c r="D3" t="n">
-        <v>16486</v>
+        <v>12781</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4649</v>
+        <v>3824</v>
       </c>
       <c r="C4" t="n">
-        <v>6643</v>
+        <v>7331</v>
       </c>
       <c r="D4" t="n">
-        <v>13932</v>
+        <v>9922</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2989</v>
+        <v>2598</v>
       </c>
       <c r="C5" t="n">
-        <v>6514</v>
+        <v>8935</v>
       </c>
       <c r="D5" t="n">
-        <v>6201</v>
+        <v>4531</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1417</v>
+        <v>1322</v>
       </c>
       <c r="C6" t="n">
-        <v>4984</v>
+        <v>7030</v>
       </c>
       <c r="D6" t="n">
-        <v>1860</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="C7" t="n">
-        <v>3109</v>
+        <v>3687</v>
       </c>
       <c r="D7" t="n">
-        <v>684</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1567</v>
+        <v>1463</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>552</v>
+        <v>468</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3636</v>
+        <v>3097</v>
       </c>
       <c r="C2" t="n">
-        <v>2774</v>
+        <v>3193</v>
       </c>
       <c r="D2" t="n">
-        <v>11466</v>
+        <v>8362</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4044</v>
+        <v>3429</v>
       </c>
       <c r="C3" t="n">
-        <v>4617</v>
+        <v>4481</v>
       </c>
       <c r="D3" t="n">
-        <v>15496</v>
+        <v>11852</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4183</v>
+        <v>3498</v>
       </c>
       <c r="C4" t="n">
-        <v>5943</v>
+        <v>5972</v>
       </c>
       <c r="D4" t="n">
-        <v>13985</v>
+        <v>10099</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3313</v>
+        <v>2805</v>
       </c>
       <c r="C5" t="n">
-        <v>6675</v>
+        <v>8507</v>
       </c>
       <c r="D5" t="n">
-        <v>7022</v>
+        <v>5101</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1685</v>
+        <v>1561</v>
       </c>
       <c r="C6" t="n">
-        <v>5664</v>
+        <v>7911</v>
       </c>
       <c r="D6" t="n">
-        <v>2249</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>336</v>
       </c>
       <c r="C7" t="n">
-        <v>3780</v>
+        <v>4757</v>
       </c>
       <c r="D7" t="n">
-        <v>784</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1968</v>
+        <v>1963</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>643</v>
+        <v>552</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6331</v>
+        <v>4194</v>
       </c>
       <c r="C2" t="n">
-        <v>4411</v>
+        <v>5893</v>
       </c>
       <c r="D2" t="n">
-        <v>14735</v>
+        <v>9156</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3281</v>
+        <v>2786</v>
       </c>
       <c r="C3" t="n">
-        <v>3480</v>
+        <v>3532</v>
       </c>
       <c r="D3" t="n">
-        <v>14020</v>
+        <v>10674</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3592</v>
+        <v>3048</v>
       </c>
       <c r="C4" t="n">
-        <v>5259</v>
+        <v>5217</v>
       </c>
       <c r="D4" t="n">
-        <v>13777</v>
+        <v>10044</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3323</v>
+        <v>2771</v>
       </c>
       <c r="C5" t="n">
-        <v>6241</v>
+        <v>7307</v>
       </c>
       <c r="D5" t="n">
-        <v>7744</v>
+        <v>5617</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2069</v>
+        <v>1841</v>
       </c>
       <c r="C6" t="n">
-        <v>6004</v>
+        <v>8073</v>
       </c>
       <c r="D6" t="n">
-        <v>2793</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>697</v>
+        <v>636</v>
       </c>
       <c r="C7" t="n">
-        <v>4480</v>
+        <v>5929</v>
       </c>
       <c r="D7" t="n">
-        <v>962</v>
+        <v>864</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>2625</v>
+        <v>2967</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1071</v>
+        <v>1013</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>356</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" t="n">
         <v>38</v>
-      </c>
-      <c r="D14" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9129</v>
+        <v>5650</v>
       </c>
       <c r="C2" t="n">
-        <v>8573</v>
+        <v>2236</v>
       </c>
       <c r="D2" t="n">
-        <v>11513</v>
+        <v>10434</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4530</v>
+        <v>3004</v>
       </c>
       <c r="C2" t="n">
-        <v>2505</v>
+        <v>3394</v>
       </c>
       <c r="D2" t="n">
-        <v>10844</v>
+        <v>6738</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4484</v>
+        <v>3729</v>
       </c>
       <c r="C3" t="n">
-        <v>3996</v>
+        <v>4371</v>
       </c>
       <c r="D3" t="n">
-        <v>15328</v>
+        <v>11507</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4906</v>
+        <v>4093</v>
       </c>
       <c r="C4" t="n">
-        <v>7333</v>
+        <v>7662</v>
       </c>
       <c r="D4" t="n">
-        <v>14158</v>
+        <v>10315</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2003</v>
+        <v>1777</v>
       </c>
       <c r="C5" t="n">
-        <v>8781</v>
+        <v>11029</v>
       </c>
       <c r="D5" t="n">
-        <v>6944</v>
+        <v>5123</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>644</v>
+        <v>587</v>
       </c>
       <c r="C6" t="n">
-        <v>5567</v>
+        <v>7392</v>
       </c>
       <c r="D6" t="n">
-        <v>2188</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>2572</v>
+        <v>2907</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1049</v>
+        <v>992</v>
       </c>
       <c r="D8" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>348</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>39</v>
+      </c>
+      <c r="D13" t="n">
         <v>37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8528</v>
+        <v>6866</v>
       </c>
       <c r="C2" t="n">
-        <v>5423</v>
+        <v>6175</v>
       </c>
       <c r="D2" t="n">
-        <v>17645</v>
+        <v>10966</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3876</v>
+        <v>2401</v>
       </c>
       <c r="C3" t="n">
-        <v>4320</v>
+        <v>1144</v>
       </c>
       <c r="D3" t="n">
-        <v>2573</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5576</v>
+        <v>6289</v>
       </c>
       <c r="C2" t="n">
-        <v>3890</v>
+        <v>5050</v>
       </c>
       <c r="D2" t="n">
-        <v>17679</v>
+        <v>17885</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5097</v>
+        <v>3803</v>
       </c>
       <c r="C3" t="n">
-        <v>4263</v>
+        <v>3480</v>
       </c>
       <c r="D3" t="n">
-        <v>4915</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1718</v>
+        <v>1076</v>
       </c>
       <c r="C4" t="n">
-        <v>2575</v>
+        <v>724</v>
       </c>
       <c r="D4" t="n">
-        <v>1699</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6286</v>
+        <v>5527</v>
       </c>
       <c r="C2" t="n">
-        <v>4834</v>
+        <v>5193</v>
       </c>
       <c r="D2" t="n">
-        <v>32592</v>
+        <v>17813</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4400</v>
+        <v>4168</v>
       </c>
       <c r="C3" t="n">
-        <v>3554</v>
+        <v>3753</v>
       </c>
       <c r="D3" t="n">
-        <v>6603</v>
+        <v>5669</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2903</v>
+        <v>2064</v>
       </c>
       <c r="C4" t="n">
-        <v>3436</v>
+        <v>2262</v>
       </c>
       <c r="D4" t="n">
-        <v>2264</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="5">
@@ -5176,10 +5176,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>750</v>
+        <v>502</v>
       </c>
       <c r="C5" t="n">
-        <v>1506</v>
+        <v>496</v>
       </c>
       <c r="D5" t="n">
         <v>1241</v>
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
         <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6632</v>
+        <v>7843</v>
       </c>
       <c r="C2" t="n">
-        <v>5184</v>
+        <v>10821</v>
       </c>
       <c r="D2" t="n">
-        <v>33987</v>
+        <v>20493</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4337</v>
+        <v>4004</v>
       </c>
       <c r="C3" t="n">
-        <v>3662</v>
+        <v>3917</v>
       </c>
       <c r="D3" t="n">
-        <v>10088</v>
+        <v>7115</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3084</v>
+        <v>2618</v>
       </c>
       <c r="C4" t="n">
-        <v>3393</v>
+        <v>3030</v>
       </c>
       <c r="D4" t="n">
-        <v>2986</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1508</v>
+        <v>1068</v>
       </c>
       <c r="C5" t="n">
-        <v>2475</v>
+        <v>1413</v>
       </c>
       <c r="D5" t="n">
-        <v>1368</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>377</v>
+        <v>280</v>
       </c>
       <c r="C6" t="n">
-        <v>901</v>
+        <v>399</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>945</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7957</v>
+        <v>7641</v>
       </c>
       <c r="C2" t="n">
-        <v>7771</v>
+        <v>9083</v>
       </c>
       <c r="D2" t="n">
-        <v>38793</v>
+        <v>22326</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3963</v>
+        <v>4286</v>
       </c>
       <c r="C3" t="n">
-        <v>3627</v>
+        <v>6151</v>
       </c>
       <c r="D3" t="n">
-        <v>12239</v>
+        <v>8135</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2306</v>
+        <v>2054</v>
       </c>
       <c r="C4" t="n">
-        <v>2869</v>
+        <v>2893</v>
       </c>
       <c r="D4" t="n">
-        <v>3658</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1194</v>
+        <v>969</v>
       </c>
       <c r="C5" t="n">
-        <v>2152</v>
+        <v>1650</v>
       </c>
       <c r="D5" t="n">
-        <v>1290</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>442</v>
+        <v>320</v>
       </c>
       <c r="C6" t="n">
-        <v>1124</v>
+        <v>619</v>
       </c>
       <c r="D6" t="n">
-        <v>779</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>395</v>
+        <v>239</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
         <v>273</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6028,7 +6028,7 @@
         <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8327</v>
+        <v>6006</v>
       </c>
       <c r="C2" t="n">
-        <v>4631</v>
+        <v>7642</v>
       </c>
       <c r="D2" t="n">
-        <v>32220</v>
+        <v>18638</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4930</v>
+        <v>4980</v>
       </c>
       <c r="C3" t="n">
-        <v>5204</v>
+        <v>6789</v>
       </c>
       <c r="D3" t="n">
-        <v>15799</v>
+        <v>10020</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2718</v>
+        <v>2811</v>
       </c>
       <c r="C4" t="n">
-        <v>3267</v>
+        <v>4865</v>
       </c>
       <c r="D4" t="n">
-        <v>5241</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1564</v>
+        <v>1357</v>
       </c>
       <c r="C5" t="n">
-        <v>2527</v>
+        <v>2367</v>
       </c>
       <c r="D5" t="n">
-        <v>1728</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>757</v>
+        <v>598</v>
       </c>
       <c r="C6" t="n">
-        <v>1692</v>
+        <v>1214</v>
       </c>
       <c r="D6" t="n">
-        <v>866</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>802</v>
+        <v>458</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>315</v>
+        <v>232</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7544</v>
+        <v>5008</v>
       </c>
       <c r="C2" t="n">
-        <v>2903</v>
+        <v>6727</v>
       </c>
       <c r="D2" t="n">
-        <v>32076</v>
+        <v>18592</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5448</v>
+        <v>4523</v>
       </c>
       <c r="C3" t="n">
-        <v>4247</v>
+        <v>6275</v>
       </c>
       <c r="D3" t="n">
-        <v>17288</v>
+        <v>10677</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3243</v>
+        <v>3342</v>
       </c>
       <c r="C4" t="n">
-        <v>4277</v>
+        <v>5872</v>
       </c>
       <c r="D4" t="n">
-        <v>7108</v>
+        <v>4919</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1883</v>
+        <v>1838</v>
       </c>
       <c r="C5" t="n">
-        <v>2848</v>
+        <v>3685</v>
       </c>
       <c r="D5" t="n">
-        <v>2299</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1042</v>
+        <v>893</v>
       </c>
       <c r="C6" t="n">
-        <v>2113</v>
+        <v>1830</v>
       </c>
       <c r="D6" t="n">
-        <v>1011</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>439</v>
+        <v>346</v>
       </c>
       <c r="C7" t="n">
-        <v>1263</v>
+        <v>865</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>555</v>
+        <v>349</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>260</v>
+        <v>221</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_33_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_33_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6047</v>
+        <v>5399</v>
       </c>
       <c r="C2" t="n">
-        <v>11316</v>
+        <v>11113</v>
       </c>
       <c r="D2" t="n">
-        <v>26050</v>
+        <v>30182</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3963</v>
+        <v>3507</v>
       </c>
       <c r="C3" t="n">
-        <v>5664</v>
+        <v>7852</v>
       </c>
       <c r="D3" t="n">
-        <v>11128</v>
+        <v>12774</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3338</v>
+        <v>2952</v>
       </c>
       <c r="C4" t="n">
-        <v>5966</v>
+        <v>6081</v>
       </c>
       <c r="D4" t="n">
-        <v>5819</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2232</v>
+        <v>1881</v>
       </c>
       <c r="C5" t="n">
-        <v>4742</v>
+        <v>4310</v>
       </c>
       <c r="D5" t="n">
-        <v>2366</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1225</v>
+        <v>1064</v>
       </c>
       <c r="C6" t="n">
-        <v>2718</v>
+        <v>2505</v>
       </c>
       <c r="D6" t="n">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>535</v>
+        <v>503</v>
       </c>
       <c r="C7" t="n">
-        <v>1346</v>
+        <v>1790</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C8" t="n">
-        <v>596</v>
+        <v>944</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>417</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8316</v>
+        <v>6642</v>
       </c>
       <c r="C2" t="n">
-        <v>9277</v>
+        <v>10740</v>
       </c>
       <c r="D2" t="n">
-        <v>25210</v>
+        <v>26764</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4038</v>
+        <v>3547</v>
       </c>
       <c r="C3" t="n">
-        <v>7281</v>
+        <v>8214</v>
       </c>
       <c r="D3" t="n">
-        <v>12409</v>
+        <v>14283</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3096</v>
+        <v>2764</v>
       </c>
       <c r="C4" t="n">
-        <v>5636</v>
+        <v>6746</v>
       </c>
       <c r="D4" t="n">
-        <v>6452</v>
+        <v>7073</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2403</v>
+        <v>2066</v>
       </c>
       <c r="C5" t="n">
-        <v>5230</v>
+        <v>5053</v>
       </c>
       <c r="D5" t="n">
-        <v>2857</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1515</v>
+        <v>1287</v>
       </c>
       <c r="C6" t="n">
-        <v>3623</v>
+        <v>3270</v>
       </c>
       <c r="D6" t="n">
-        <v>1271</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>752</v>
+        <v>671</v>
       </c>
       <c r="C7" t="n">
-        <v>1950</v>
+        <v>2111</v>
       </c>
       <c r="D7" t="n">
-        <v>718</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="C8" t="n">
-        <v>926</v>
+        <v>1299</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>408</v>
+        <v>638</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>299</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9259</v>
+        <v>8022</v>
       </c>
       <c r="C2" t="n">
-        <v>12509</v>
+        <v>10096</v>
       </c>
       <c r="D2" t="n">
-        <v>25541</v>
+        <v>29052</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4693</v>
+        <v>3892</v>
       </c>
       <c r="C3" t="n">
-        <v>7192</v>
+        <v>8210</v>
       </c>
       <c r="D3" t="n">
-        <v>13233</v>
+        <v>15080</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2977</v>
+        <v>2631</v>
       </c>
       <c r="C4" t="n">
-        <v>6260</v>
+        <v>7253</v>
       </c>
       <c r="D4" t="n">
-        <v>7170</v>
+        <v>7828</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2423</v>
+        <v>2112</v>
       </c>
       <c r="C5" t="n">
-        <v>5246</v>
+        <v>5614</v>
       </c>
       <c r="D5" t="n">
-        <v>3260</v>
+        <v>3445</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1709</v>
+        <v>1453</v>
       </c>
       <c r="C6" t="n">
-        <v>4268</v>
+        <v>3976</v>
       </c>
       <c r="D6" t="n">
-        <v>1482</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>948</v>
+        <v>819</v>
       </c>
       <c r="C7" t="n">
-        <v>2618</v>
+        <v>2555</v>
       </c>
       <c r="D7" t="n">
-        <v>779</v>
+        <v>769</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>420</v>
+        <v>382</v>
       </c>
       <c r="C8" t="n">
-        <v>1327</v>
+        <v>1604</v>
       </c>
       <c r="D8" t="n">
-        <v>493</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C9" t="n">
-        <v>610</v>
+        <v>890</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>295</v>
+        <v>418</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8418</v>
+        <v>7288</v>
       </c>
       <c r="C2" t="n">
-        <v>8406</v>
+        <v>6865</v>
       </c>
       <c r="D2" t="n">
-        <v>20940</v>
+        <v>23965</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5535</v>
+        <v>4695</v>
       </c>
       <c r="C3" t="n">
-        <v>11029</v>
+        <v>12087</v>
       </c>
       <c r="D3" t="n">
-        <v>14329</v>
+        <v>16157</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2238</v>
+        <v>1951</v>
       </c>
       <c r="C4" t="n">
-        <v>8521</v>
+        <v>9358</v>
       </c>
       <c r="D4" t="n">
-        <v>6971</v>
+        <v>7491</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1579</v>
+        <v>1342</v>
       </c>
       <c r="C5" t="n">
-        <v>4182</v>
+        <v>3896</v>
       </c>
       <c r="D5" t="n">
-        <v>2359</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>875</v>
+        <v>756</v>
       </c>
       <c r="C6" t="n">
-        <v>2565</v>
+        <v>2503</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>388</v>
+        <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>1300</v>
+        <v>1571</v>
       </c>
       <c r="D7" t="n">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C8" t="n">
-        <v>597</v>
+        <v>872</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>409</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5052</v>
+        <v>4577</v>
       </c>
       <c r="C2" t="n">
-        <v>4477</v>
+        <v>4085</v>
       </c>
       <c r="D2" t="n">
-        <v>15797</v>
+        <v>16756</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5826</v>
+        <v>4972</v>
       </c>
       <c r="C3" t="n">
-        <v>8896</v>
+        <v>8834</v>
       </c>
       <c r="D3" t="n">
-        <v>14402</v>
+        <v>16288</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3061</v>
+        <v>2606</v>
       </c>
       <c r="C4" t="n">
-        <v>9768</v>
+        <v>10690</v>
       </c>
       <c r="D4" t="n">
-        <v>8023</v>
+        <v>8738</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1750</v>
+        <v>1494</v>
       </c>
       <c r="C5" t="n">
-        <v>6128</v>
+        <v>6256</v>
       </c>
       <c r="D5" t="n">
-        <v>2908</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1052</v>
+        <v>895</v>
       </c>
       <c r="C6" t="n">
-        <v>3295</v>
+        <v>3137</v>
       </c>
       <c r="D6" t="n">
-        <v>929</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>363</v>
+        <v>332</v>
       </c>
       <c r="C7" t="n">
-        <v>1748</v>
+        <v>1940</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>810</v>
+        <v>1122</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>338</v>
+        <v>454</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6314</v>
+        <v>5333</v>
       </c>
       <c r="C2" t="n">
-        <v>6252</v>
+        <v>8565</v>
       </c>
       <c r="D2" t="n">
-        <v>17545</v>
+        <v>19462</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4616</v>
+        <v>4037</v>
       </c>
       <c r="C3" t="n">
-        <v>5997</v>
+        <v>5854</v>
       </c>
       <c r="D3" t="n">
-        <v>13750</v>
+        <v>15257</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3675</v>
+        <v>3091</v>
       </c>
       <c r="C4" t="n">
-        <v>9129</v>
+        <v>9558</v>
       </c>
       <c r="D4" t="n">
-        <v>8743</v>
+        <v>9704</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2051</v>
+        <v>1749</v>
       </c>
       <c r="C5" t="n">
-        <v>7806</v>
+        <v>8271</v>
       </c>
       <c r="D5" t="n">
-        <v>3654</v>
+        <v>3809</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1233</v>
+        <v>1059</v>
       </c>
       <c r="C6" t="n">
-        <v>4540</v>
+        <v>4484</v>
       </c>
       <c r="D6" t="n">
-        <v>1220</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>558</v>
+        <v>482</v>
       </c>
       <c r="C7" t="n">
-        <v>2446</v>
+        <v>2474</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C8" t="n">
-        <v>1203</v>
+        <v>1461</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>521</v>
+        <v>707</v>
       </c>
       <c r="D9" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>264</v>
+        <v>315</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3743</v>
+        <v>3186</v>
       </c>
       <c r="C2" t="n">
-        <v>2906</v>
+        <v>4022</v>
       </c>
       <c r="D2" t="n">
-        <v>12093</v>
+        <v>13557</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4847</v>
+        <v>4186</v>
       </c>
       <c r="C3" t="n">
-        <v>5892</v>
+        <v>6586</v>
       </c>
       <c r="D3" t="n">
-        <v>13977</v>
+        <v>15352</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4060</v>
+        <v>3420</v>
       </c>
       <c r="C4" t="n">
-        <v>8850</v>
+        <v>9159</v>
       </c>
       <c r="D4" t="n">
-        <v>9364</v>
+        <v>10391</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2154</v>
+        <v>1824</v>
       </c>
       <c r="C5" t="n">
-        <v>9194</v>
+        <v>9733</v>
       </c>
       <c r="D5" t="n">
-        <v>3856</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1016</v>
+        <v>875</v>
       </c>
       <c r="C6" t="n">
-        <v>5443</v>
+        <v>5327</v>
       </c>
       <c r="D6" t="n">
-        <v>1207</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>2431</v>
+        <v>2612</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>887</v>
+        <v>1136</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4268</v>
+        <v>3533</v>
       </c>
       <c r="C2" t="n">
-        <v>6278</v>
+        <v>9221</v>
       </c>
       <c r="D2" t="n">
-        <v>10837</v>
+        <v>11852</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3746</v>
+        <v>3220</v>
       </c>
       <c r="C3" t="n">
-        <v>3990</v>
+        <v>4833</v>
       </c>
       <c r="D3" t="n">
-        <v>12781</v>
+        <v>14223</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3824</v>
+        <v>3284</v>
       </c>
       <c r="C4" t="n">
-        <v>7331</v>
+        <v>7846</v>
       </c>
       <c r="D4" t="n">
-        <v>9922</v>
+        <v>10837</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2598</v>
+        <v>2182</v>
       </c>
       <c r="C5" t="n">
-        <v>8935</v>
+        <v>9370</v>
       </c>
       <c r="D5" t="n">
-        <v>4531</v>
+        <v>4823</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1322</v>
+        <v>1112</v>
       </c>
       <c r="C6" t="n">
-        <v>7030</v>
+        <v>7150</v>
       </c>
       <c r="D6" t="n">
-        <v>1547</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>373</v>
+        <v>332</v>
       </c>
       <c r="C7" t="n">
-        <v>3687</v>
+        <v>3726</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>1463</v>
+        <v>1678</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>468</v>
+        <v>576</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3097</v>
+        <v>2444</v>
       </c>
       <c r="C2" t="n">
-        <v>3193</v>
+        <v>4697</v>
       </c>
       <c r="D2" t="n">
-        <v>8362</v>
+        <v>8878</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3429</v>
+        <v>2908</v>
       </c>
       <c r="C3" t="n">
-        <v>4481</v>
+        <v>5983</v>
       </c>
       <c r="D3" t="n">
-        <v>11852</v>
+        <v>13301</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3498</v>
+        <v>2978</v>
       </c>
       <c r="C4" t="n">
-        <v>5972</v>
+        <v>6647</v>
       </c>
       <c r="D4" t="n">
-        <v>10099</v>
+        <v>11034</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2805</v>
+        <v>2389</v>
       </c>
       <c r="C5" t="n">
-        <v>8507</v>
+        <v>8993</v>
       </c>
       <c r="D5" t="n">
-        <v>5101</v>
+        <v>5357</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1561</v>
+        <v>1297</v>
       </c>
       <c r="C6" t="n">
-        <v>7911</v>
+        <v>8113</v>
       </c>
       <c r="D6" t="n">
-        <v>1816</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="C7" t="n">
-        <v>4757</v>
+        <v>4785</v>
       </c>
       <c r="D7" t="n">
-        <v>746</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1963</v>
+        <v>2154</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>552</v>
+        <v>652</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
         <v>177</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4194</v>
+        <v>3335</v>
       </c>
       <c r="C2" t="n">
-        <v>5893</v>
+        <v>9712</v>
       </c>
       <c r="D2" t="n">
-        <v>9156</v>
+        <v>13377</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2786</v>
+        <v>2314</v>
       </c>
       <c r="C3" t="n">
-        <v>3532</v>
+        <v>4927</v>
       </c>
       <c r="D3" t="n">
-        <v>10674</v>
+        <v>11918</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3048</v>
+        <v>2567</v>
       </c>
       <c r="C4" t="n">
-        <v>5217</v>
+        <v>6234</v>
       </c>
       <c r="D4" t="n">
-        <v>10044</v>
+        <v>11025</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2771</v>
+        <v>2382</v>
       </c>
       <c r="C5" t="n">
-        <v>7307</v>
+        <v>7882</v>
       </c>
       <c r="D5" t="n">
-        <v>5617</v>
+        <v>5957</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1841</v>
+        <v>1537</v>
       </c>
       <c r="C6" t="n">
-        <v>8073</v>
+        <v>8375</v>
       </c>
       <c r="D6" t="n">
-        <v>2202</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>636</v>
+        <v>531</v>
       </c>
       <c r="C7" t="n">
-        <v>5929</v>
+        <v>5989</v>
       </c>
       <c r="D7" t="n">
-        <v>864</v>
+        <v>845</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>2967</v>
+        <v>3076</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1013</v>
+        <v>1122</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="D10" t="n">
         <v>185</v>
@@ -3711,7 +3711,7 @@
         <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5650</v>
+        <v>6080</v>
       </c>
       <c r="C2" t="n">
-        <v>2236</v>
+        <v>9115</v>
       </c>
       <c r="D2" t="n">
-        <v>10434</v>
+        <v>8822</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3004</v>
+        <v>2413</v>
       </c>
       <c r="C2" t="n">
-        <v>3394</v>
+        <v>5672</v>
       </c>
       <c r="D2" t="n">
-        <v>6738</v>
+        <v>9952</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3729</v>
+        <v>3091</v>
       </c>
       <c r="C3" t="n">
-        <v>4371</v>
+        <v>6402</v>
       </c>
       <c r="D3" t="n">
-        <v>11507</v>
+        <v>12931</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4093</v>
+        <v>3491</v>
       </c>
       <c r="C4" t="n">
-        <v>7662</v>
+        <v>8983</v>
       </c>
       <c r="D4" t="n">
-        <v>10315</v>
+        <v>11272</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1777</v>
+        <v>1464</v>
       </c>
       <c r="C5" t="n">
-        <v>11029</v>
+        <v>11642</v>
       </c>
       <c r="D5" t="n">
-        <v>5123</v>
+        <v>5429</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>587</v>
+        <v>490</v>
       </c>
       <c r="C6" t="n">
-        <v>7392</v>
+        <v>7428</v>
       </c>
       <c r="D6" t="n">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>2907</v>
+        <v>3014</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>992</v>
+        <v>1099</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="D9" t="n">
         <v>181</v>
@@ -4319,7 +4319,7 @@
         <v>155</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6866</v>
+        <v>7294</v>
       </c>
       <c r="C2" t="n">
-        <v>6175</v>
+        <v>5355</v>
       </c>
       <c r="D2" t="n">
-        <v>10966</v>
+        <v>11242</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2401</v>
+        <v>2583</v>
       </c>
       <c r="C3" t="n">
-        <v>1144</v>
+        <v>4593</v>
       </c>
       <c r="D3" t="n">
-        <v>2392</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6289</v>
+        <v>4894</v>
       </c>
       <c r="C2" t="n">
-        <v>5050</v>
+        <v>4336</v>
       </c>
       <c r="D2" t="n">
-        <v>17885</v>
+        <v>21769</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3803</v>
+        <v>4054</v>
       </c>
       <c r="C3" t="n">
-        <v>3480</v>
+        <v>4332</v>
       </c>
       <c r="D3" t="n">
-        <v>3656</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1076</v>
+        <v>1156</v>
       </c>
       <c r="C4" t="n">
-        <v>724</v>
+        <v>2734</v>
       </c>
       <c r="D4" t="n">
-        <v>1663</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5527</v>
+        <v>4274</v>
       </c>
       <c r="C2" t="n">
-        <v>5193</v>
+        <v>4964</v>
       </c>
       <c r="D2" t="n">
-        <v>17813</v>
+        <v>22604</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4168</v>
+        <v>3679</v>
       </c>
       <c r="C3" t="n">
-        <v>3753</v>
+        <v>3751</v>
       </c>
       <c r="D3" t="n">
-        <v>5669</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2064</v>
+        <v>2214</v>
       </c>
       <c r="C4" t="n">
-        <v>2262</v>
+        <v>3582</v>
       </c>
       <c r="D4" t="n">
-        <v>1979</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>502</v>
+        <v>525</v>
       </c>
       <c r="C5" t="n">
-        <v>496</v>
+        <v>1591</v>
       </c>
       <c r="D5" t="n">
-        <v>1241</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7843</v>
+        <v>6491</v>
       </c>
       <c r="C2" t="n">
-        <v>10821</v>
+        <v>4263</v>
       </c>
       <c r="D2" t="n">
-        <v>20493</v>
+        <v>20432</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4004</v>
+        <v>3268</v>
       </c>
       <c r="C3" t="n">
-        <v>3917</v>
+        <v>3808</v>
       </c>
       <c r="D3" t="n">
-        <v>7115</v>
+        <v>8232</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2618</v>
+        <v>2510</v>
       </c>
       <c r="C4" t="n">
-        <v>3030</v>
+        <v>3598</v>
       </c>
       <c r="D4" t="n">
-        <v>2572</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1068</v>
+        <v>1120</v>
       </c>
       <c r="C5" t="n">
-        <v>1413</v>
+        <v>2574</v>
       </c>
       <c r="D5" t="n">
-        <v>1337</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C6" t="n">
-        <v>399</v>
+        <v>954</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7641</v>
+        <v>6890</v>
       </c>
       <c r="C2" t="n">
-        <v>9083</v>
+        <v>13473</v>
       </c>
       <c r="D2" t="n">
-        <v>22326</v>
+        <v>20108</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4286</v>
+        <v>3501</v>
       </c>
       <c r="C3" t="n">
-        <v>6151</v>
+        <v>3310</v>
       </c>
       <c r="D3" t="n">
-        <v>8135</v>
+        <v>8944</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2054</v>
+        <v>1783</v>
       </c>
       <c r="C4" t="n">
-        <v>2893</v>
+        <v>3014</v>
       </c>
       <c r="D4" t="n">
-        <v>2877</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>969</v>
+        <v>952</v>
       </c>
       <c r="C5" t="n">
-        <v>1650</v>
+        <v>2274</v>
       </c>
       <c r="D5" t="n">
-        <v>1233</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="C6" t="n">
-        <v>619</v>
+        <v>1193</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>769</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>239</v>
+        <v>411</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6006</v>
+        <v>5513</v>
       </c>
       <c r="C2" t="n">
-        <v>7642</v>
+        <v>7165</v>
       </c>
       <c r="D2" t="n">
-        <v>18638</v>
+        <v>21741</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4980</v>
+        <v>4323</v>
       </c>
       <c r="C3" t="n">
-        <v>6789</v>
+        <v>8042</v>
       </c>
       <c r="D3" t="n">
-        <v>10020</v>
+        <v>10236</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2811</v>
+        <v>2325</v>
       </c>
       <c r="C4" t="n">
-        <v>4865</v>
+        <v>3133</v>
       </c>
       <c r="D4" t="n">
-        <v>3900</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1357</v>
+        <v>1214</v>
       </c>
       <c r="C5" t="n">
-        <v>2367</v>
+        <v>2667</v>
       </c>
       <c r="D5" t="n">
-        <v>1515</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="6">
@@ -6126,10 +6126,10 @@
         <v>598</v>
       </c>
       <c r="C6" t="n">
-        <v>1214</v>
+        <v>1800</v>
       </c>
       <c r="D6" t="n">
-        <v>846</v>
+        <v>831</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C7" t="n">
-        <v>458</v>
+        <v>855</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>232</v>
+        <v>326</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5008</v>
+        <v>4427</v>
       </c>
       <c r="C2" t="n">
-        <v>6727</v>
+        <v>11418</v>
       </c>
       <c r="D2" t="n">
-        <v>18592</v>
+        <v>26035</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4523</v>
+        <v>4083</v>
       </c>
       <c r="C3" t="n">
-        <v>6275</v>
+        <v>6547</v>
       </c>
       <c r="D3" t="n">
-        <v>10677</v>
+        <v>11339</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3342</v>
+        <v>2834</v>
       </c>
       <c r="C4" t="n">
-        <v>5872</v>
+        <v>5818</v>
       </c>
       <c r="D4" t="n">
-        <v>4919</v>
+        <v>5233</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1838</v>
+        <v>1556</v>
       </c>
       <c r="C5" t="n">
-        <v>3685</v>
+        <v>2870</v>
       </c>
       <c r="D5" t="n">
-        <v>1926</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>893</v>
+        <v>819</v>
       </c>
       <c r="C6" t="n">
-        <v>1830</v>
+        <v>2245</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C7" t="n">
-        <v>865</v>
+        <v>1354</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>349</v>
+        <v>592</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_33_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_33_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5399</v>
+        <v>961</v>
       </c>
       <c r="C2" t="n">
-        <v>11113</v>
+        <v>3725</v>
       </c>
       <c r="D2" t="n">
-        <v>30182</v>
+        <v>16823</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3507</v>
+        <v>1725</v>
       </c>
       <c r="C3" t="n">
-        <v>7852</v>
+        <v>7641</v>
       </c>
       <c r="D3" t="n">
-        <v>12774</v>
+        <v>14696</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2952</v>
+        <v>1346</v>
       </c>
       <c r="C4" t="n">
-        <v>6081</v>
+        <v>7881</v>
       </c>
       <c r="D4" t="n">
-        <v>6187</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1881</v>
+        <v>813</v>
       </c>
       <c r="C5" t="n">
-        <v>4310</v>
+        <v>3855</v>
       </c>
       <c r="D5" t="n">
-        <v>2510</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1064</v>
+        <v>352</v>
       </c>
       <c r="C6" t="n">
-        <v>2505</v>
+        <v>1522</v>
       </c>
       <c r="D6" t="n">
-        <v>1100</v>
+        <v>721</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>503</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>1790</v>
+        <v>600</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>944</v>
+        <v>342</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>417</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>37</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6642</v>
+        <v>1469</v>
       </c>
       <c r="C2" t="n">
-        <v>10740</v>
+        <v>5466</v>
       </c>
       <c r="D2" t="n">
-        <v>26764</v>
+        <v>15960</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3547</v>
+        <v>1147</v>
       </c>
       <c r="C3" t="n">
-        <v>8214</v>
+        <v>4839</v>
       </c>
       <c r="D3" t="n">
-        <v>14283</v>
+        <v>14119</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2764</v>
+        <v>1332</v>
       </c>
       <c r="C4" t="n">
-        <v>6746</v>
+        <v>7659</v>
       </c>
       <c r="D4" t="n">
-        <v>7073</v>
+        <v>7041</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2066</v>
+        <v>947</v>
       </c>
       <c r="C5" t="n">
-        <v>5053</v>
+        <v>5900</v>
       </c>
       <c r="D5" t="n">
-        <v>2974</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1287</v>
+        <v>512</v>
       </c>
       <c r="C6" t="n">
-        <v>3270</v>
+        <v>2707</v>
       </c>
       <c r="D6" t="n">
-        <v>1301</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>671</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>2111</v>
+        <v>1057</v>
       </c>
       <c r="D7" t="n">
-        <v>701</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1299</v>
+        <v>467</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>638</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8022</v>
+        <v>773</v>
       </c>
       <c r="C2" t="n">
-        <v>10096</v>
+        <v>2206</v>
       </c>
       <c r="D2" t="n">
-        <v>29052</v>
+        <v>10763</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3892</v>
+        <v>1193</v>
       </c>
       <c r="C3" t="n">
-        <v>8210</v>
+        <v>4880</v>
       </c>
       <c r="D3" t="n">
-        <v>15080</v>
+        <v>13970</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2631</v>
+        <v>1461</v>
       </c>
       <c r="C4" t="n">
-        <v>7253</v>
+        <v>7171</v>
       </c>
       <c r="D4" t="n">
-        <v>7828</v>
+        <v>7980</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2112</v>
+        <v>985</v>
       </c>
       <c r="C5" t="n">
-        <v>5614</v>
+        <v>7116</v>
       </c>
       <c r="D5" t="n">
-        <v>3445</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1453</v>
+        <v>404</v>
       </c>
       <c r="C6" t="n">
-        <v>3976</v>
+        <v>3601</v>
       </c>
       <c r="D6" t="n">
-        <v>1524</v>
+        <v>907</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>819</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>2555</v>
+        <v>1054</v>
       </c>
       <c r="D7" t="n">
-        <v>769</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>382</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1604</v>
+        <v>477</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>890</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>418</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7288</v>
+        <v>766</v>
       </c>
       <c r="C2" t="n">
-        <v>6865</v>
+        <v>5826</v>
       </c>
       <c r="D2" t="n">
-        <v>23965</v>
+        <v>10466</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4695</v>
+        <v>843</v>
       </c>
       <c r="C3" t="n">
-        <v>12087</v>
+        <v>3067</v>
       </c>
       <c r="D3" t="n">
-        <v>16157</v>
+        <v>12499</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1951</v>
+        <v>1191</v>
       </c>
       <c r="C4" t="n">
-        <v>9358</v>
+        <v>5859</v>
       </c>
       <c r="D4" t="n">
-        <v>7491</v>
+        <v>8906</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1342</v>
+        <v>1083</v>
       </c>
       <c r="C5" t="n">
-        <v>3896</v>
+        <v>7064</v>
       </c>
       <c r="D5" t="n">
-        <v>2419</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>756</v>
+        <v>590</v>
       </c>
       <c r="C6" t="n">
-        <v>2503</v>
+        <v>5321</v>
       </c>
       <c r="D6" t="n">
-        <v>753</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>1571</v>
+        <v>2222</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>872</v>
+        <v>723</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>409</v>
+        <v>338</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4577</v>
+        <v>431</v>
       </c>
       <c r="C2" t="n">
-        <v>4085</v>
+        <v>2990</v>
       </c>
       <c r="D2" t="n">
-        <v>16756</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4972</v>
+        <v>710</v>
       </c>
       <c r="C3" t="n">
-        <v>8834</v>
+        <v>3925</v>
       </c>
       <c r="D3" t="n">
-        <v>16288</v>
+        <v>11502</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2606</v>
+        <v>989</v>
       </c>
       <c r="C4" t="n">
-        <v>10690</v>
+        <v>4592</v>
       </c>
       <c r="D4" t="n">
-        <v>8738</v>
+        <v>9272</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1494</v>
+        <v>1104</v>
       </c>
       <c r="C5" t="n">
-        <v>6256</v>
+        <v>6679</v>
       </c>
       <c r="D5" t="n">
-        <v>3024</v>
+        <v>4218</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>895</v>
+        <v>702</v>
       </c>
       <c r="C6" t="n">
-        <v>3137</v>
+        <v>6175</v>
       </c>
       <c r="D6" t="n">
-        <v>925</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>332</v>
+        <v>193</v>
       </c>
       <c r="C7" t="n">
-        <v>1940</v>
+        <v>3336</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1122</v>
+        <v>1094</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5333</v>
+        <v>634</v>
       </c>
       <c r="C2" t="n">
-        <v>8565</v>
+        <v>6611</v>
       </c>
       <c r="D2" t="n">
-        <v>19462</v>
+        <v>8375</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4037</v>
+        <v>499</v>
       </c>
       <c r="C3" t="n">
-        <v>5854</v>
+        <v>3090</v>
       </c>
       <c r="D3" t="n">
-        <v>15257</v>
+        <v>10152</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3091</v>
+        <v>768</v>
       </c>
       <c r="C4" t="n">
-        <v>9558</v>
+        <v>4169</v>
       </c>
       <c r="D4" t="n">
-        <v>9704</v>
+        <v>9354</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1749</v>
+        <v>981</v>
       </c>
       <c r="C5" t="n">
-        <v>8271</v>
+        <v>5622</v>
       </c>
       <c r="D5" t="n">
-        <v>3809</v>
+        <v>4866</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1059</v>
+        <v>801</v>
       </c>
       <c r="C6" t="n">
-        <v>4484</v>
+        <v>6338</v>
       </c>
       <c r="D6" t="n">
-        <v>1215</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>482</v>
+        <v>338</v>
       </c>
       <c r="C7" t="n">
-        <v>2474</v>
+        <v>4591</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>1461</v>
+        <v>2005</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>707</v>
+        <v>685</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3186</v>
+        <v>420</v>
       </c>
       <c r="C2" t="n">
-        <v>4022</v>
+        <v>3437</v>
       </c>
       <c r="D2" t="n">
-        <v>13557</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4186</v>
+        <v>720</v>
       </c>
       <c r="C3" t="n">
-        <v>6586</v>
+        <v>4283</v>
       </c>
       <c r="D3" t="n">
-        <v>15352</v>
+        <v>10767</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3420</v>
+        <v>1278</v>
       </c>
       <c r="C4" t="n">
-        <v>9159</v>
+        <v>5939</v>
       </c>
       <c r="D4" t="n">
-        <v>10391</v>
+        <v>9702</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1824</v>
+        <v>812</v>
       </c>
       <c r="C5" t="n">
-        <v>9733</v>
+        <v>8590</v>
       </c>
       <c r="D5" t="n">
-        <v>4030</v>
+        <v>4456</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>875</v>
+        <v>312</v>
       </c>
       <c r="C6" t="n">
-        <v>5327</v>
+        <v>6114</v>
       </c>
       <c r="D6" t="n">
-        <v>1198</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="C7" t="n">
-        <v>2612</v>
+        <v>1964</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1136</v>
+        <v>671</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3533</v>
+        <v>244</v>
       </c>
       <c r="C2" t="n">
-        <v>9221</v>
+        <v>2062</v>
       </c>
       <c r="D2" t="n">
-        <v>11852</v>
+        <v>4854</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3220</v>
+        <v>504</v>
       </c>
       <c r="C3" t="n">
-        <v>4833</v>
+        <v>3394</v>
       </c>
       <c r="D3" t="n">
-        <v>14223</v>
+        <v>9313</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3284</v>
+        <v>853</v>
       </c>
       <c r="C4" t="n">
-        <v>7846</v>
+        <v>4819</v>
       </c>
       <c r="D4" t="n">
-        <v>10837</v>
+        <v>9201</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2182</v>
+        <v>730</v>
       </c>
       <c r="C5" t="n">
-        <v>9370</v>
+        <v>6503</v>
       </c>
       <c r="D5" t="n">
-        <v>4823</v>
+        <v>4657</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1112</v>
+        <v>301</v>
       </c>
       <c r="C6" t="n">
-        <v>7150</v>
+        <v>5911</v>
       </c>
       <c r="D6" t="n">
-        <v>1563</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>332</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3726</v>
+        <v>2724</v>
       </c>
       <c r="D7" t="n">
-        <v>649</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1678</v>
+        <v>764</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>576</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2444</v>
+        <v>174</v>
       </c>
       <c r="C2" t="n">
-        <v>4697</v>
+        <v>4134</v>
       </c>
       <c r="D2" t="n">
-        <v>8878</v>
+        <v>8170</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2908</v>
+        <v>318</v>
       </c>
       <c r="C3" t="n">
-        <v>5983</v>
+        <v>2325</v>
       </c>
       <c r="D3" t="n">
-        <v>13301</v>
+        <v>7929</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2978</v>
+        <v>598</v>
       </c>
       <c r="C4" t="n">
-        <v>6647</v>
+        <v>3911</v>
       </c>
       <c r="D4" t="n">
-        <v>11034</v>
+        <v>8942</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2389</v>
+        <v>718</v>
       </c>
       <c r="C5" t="n">
-        <v>8993</v>
+        <v>5508</v>
       </c>
       <c r="D5" t="n">
-        <v>5357</v>
+        <v>5344</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1297</v>
+        <v>456</v>
       </c>
       <c r="C6" t="n">
-        <v>8113</v>
+        <v>6151</v>
       </c>
       <c r="D6" t="n">
-        <v>1871</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>4785</v>
+        <v>4373</v>
       </c>
       <c r="D7" t="n">
-        <v>717</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C8" t="n">
-        <v>2154</v>
+        <v>1712</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>652</v>
+        <v>496</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3335</v>
+        <v>351</v>
       </c>
       <c r="C2" t="n">
-        <v>9712</v>
+        <v>10813</v>
       </c>
       <c r="D2" t="n">
-        <v>13377</v>
+        <v>8084</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2314</v>
+        <v>211</v>
       </c>
       <c r="C3" t="n">
-        <v>4927</v>
+        <v>2845</v>
       </c>
       <c r="D3" t="n">
-        <v>11918</v>
+        <v>7418</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2567</v>
+        <v>412</v>
       </c>
       <c r="C4" t="n">
-        <v>6234</v>
+        <v>2969</v>
       </c>
       <c r="D4" t="n">
-        <v>11025</v>
+        <v>8409</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2382</v>
+        <v>603</v>
       </c>
       <c r="C5" t="n">
-        <v>7882</v>
+        <v>4580</v>
       </c>
       <c r="D5" t="n">
-        <v>5957</v>
+        <v>5803</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1537</v>
+        <v>531</v>
       </c>
       <c r="C6" t="n">
-        <v>8375</v>
+        <v>5770</v>
       </c>
       <c r="D6" t="n">
-        <v>2282</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>531</v>
+        <v>256</v>
       </c>
       <c r="C7" t="n">
-        <v>5989</v>
+        <v>5225</v>
       </c>
       <c r="D7" t="n">
-        <v>845</v>
+        <v>967</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>3076</v>
+        <v>2936</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1122</v>
+        <v>1032</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6080</v>
+        <v>6218</v>
       </c>
       <c r="C2" t="n">
-        <v>9115</v>
+        <v>6847</v>
       </c>
       <c r="D2" t="n">
-        <v>8822</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2413</v>
+        <v>314</v>
       </c>
       <c r="C2" t="n">
-        <v>5672</v>
+        <v>9237</v>
       </c>
       <c r="D2" t="n">
-        <v>9952</v>
+        <v>12818</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3091</v>
+        <v>221</v>
       </c>
       <c r="C3" t="n">
-        <v>6402</v>
+        <v>5718</v>
       </c>
       <c r="D3" t="n">
-        <v>12931</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3491</v>
+        <v>284</v>
       </c>
       <c r="C4" t="n">
-        <v>8983</v>
+        <v>2820</v>
       </c>
       <c r="D4" t="n">
-        <v>11272</v>
+        <v>7991</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1464</v>
+        <v>485</v>
       </c>
       <c r="C5" t="n">
-        <v>11642</v>
+        <v>3742</v>
       </c>
       <c r="D5" t="n">
-        <v>5429</v>
+        <v>5971</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="C6" t="n">
-        <v>7428</v>
+        <v>5132</v>
       </c>
       <c r="D6" t="n">
-        <v>1816</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>335</v>
       </c>
       <c r="C7" t="n">
-        <v>3014</v>
+        <v>5463</v>
       </c>
       <c r="D7" t="n">
-        <v>537</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>1099</v>
+        <v>3899</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>350</v>
+        <v>1786</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>155</v>
+        <v>598</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>205</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7294</v>
+        <v>4820</v>
       </c>
       <c r="C2" t="n">
-        <v>5355</v>
+        <v>6487</v>
       </c>
       <c r="D2" t="n">
-        <v>11242</v>
+        <v>13111</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2583</v>
+        <v>2052</v>
       </c>
       <c r="C3" t="n">
-        <v>4593</v>
+        <v>2703</v>
       </c>
       <c r="D3" t="n">
-        <v>2121</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4894</v>
+        <v>3472</v>
       </c>
       <c r="C2" t="n">
-        <v>4336</v>
+        <v>6792</v>
       </c>
       <c r="D2" t="n">
-        <v>21769</v>
+        <v>18265</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4054</v>
+        <v>2886</v>
       </c>
       <c r="C3" t="n">
-        <v>4332</v>
+        <v>4281</v>
       </c>
       <c r="D3" t="n">
-        <v>3497</v>
+        <v>3284</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1156</v>
+        <v>973</v>
       </c>
       <c r="C4" t="n">
-        <v>2734</v>
+        <v>1734</v>
       </c>
       <c r="D4" t="n">
-        <v>1608</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4274</v>
+        <v>1675</v>
       </c>
       <c r="C2" t="n">
-        <v>4964</v>
+        <v>4172</v>
       </c>
       <c r="D2" t="n">
-        <v>22604</v>
+        <v>24820</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3679</v>
+        <v>2624</v>
       </c>
       <c r="C3" t="n">
-        <v>3751</v>
+        <v>4943</v>
       </c>
       <c r="D3" t="n">
-        <v>6168</v>
+        <v>5559</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2214</v>
+        <v>1684</v>
       </c>
       <c r="C4" t="n">
-        <v>3582</v>
+        <v>3238</v>
       </c>
       <c r="D4" t="n">
-        <v>1921</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>525</v>
+        <v>468</v>
       </c>
       <c r="C5" t="n">
-        <v>1591</v>
+        <v>1096</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>628</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6491</v>
+        <v>1196</v>
       </c>
       <c r="C2" t="n">
-        <v>4263</v>
+        <v>3931</v>
       </c>
       <c r="D2" t="n">
-        <v>20432</v>
+        <v>21829</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3268</v>
+        <v>1787</v>
       </c>
       <c r="C3" t="n">
-        <v>3808</v>
+        <v>3900</v>
       </c>
       <c r="D3" t="n">
-        <v>8232</v>
+        <v>8240</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2510</v>
+        <v>1863</v>
       </c>
       <c r="C4" t="n">
-        <v>3598</v>
+        <v>4152</v>
       </c>
       <c r="D4" t="n">
-        <v>2637</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1120</v>
+        <v>917</v>
       </c>
       <c r="C5" t="n">
-        <v>2574</v>
+        <v>2265</v>
       </c>
       <c r="D5" t="n">
-        <v>1288</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>292</v>
+        <v>259</v>
       </c>
       <c r="C6" t="n">
-        <v>954</v>
+        <v>705</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>376</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6890</v>
+        <v>2183</v>
       </c>
       <c r="C2" t="n">
-        <v>13473</v>
+        <v>11797</v>
       </c>
       <c r="D2" t="n">
-        <v>20108</v>
+        <v>33226</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3501</v>
+        <v>1250</v>
       </c>
       <c r="C3" t="n">
-        <v>3310</v>
+        <v>3402</v>
       </c>
       <c r="D3" t="n">
-        <v>8944</v>
+        <v>9725</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1783</v>
+        <v>1587</v>
       </c>
       <c r="C4" t="n">
-        <v>3014</v>
+        <v>3927</v>
       </c>
       <c r="D4" t="n">
-        <v>3122</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>952</v>
+        <v>1204</v>
       </c>
       <c r="C5" t="n">
-        <v>2274</v>
+        <v>3192</v>
       </c>
       <c r="D5" t="n">
-        <v>1190</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>330</v>
+        <v>509</v>
       </c>
       <c r="C6" t="n">
-        <v>1193</v>
+        <v>1505</v>
       </c>
       <c r="D6" t="n">
-        <v>769</v>
+        <v>881</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>411</v>
+        <v>502</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5513</v>
+        <v>2083</v>
       </c>
       <c r="C2" t="n">
-        <v>7165</v>
+        <v>11961</v>
       </c>
       <c r="D2" t="n">
-        <v>21741</v>
+        <v>31373</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4323</v>
+        <v>1371</v>
       </c>
       <c r="C3" t="n">
-        <v>8042</v>
+        <v>6598</v>
       </c>
       <c r="D3" t="n">
-        <v>10236</v>
+        <v>12440</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2325</v>
+        <v>1249</v>
       </c>
       <c r="C4" t="n">
-        <v>3133</v>
+        <v>3573</v>
       </c>
       <c r="D4" t="n">
-        <v>4256</v>
+        <v>4316</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1214</v>
+        <v>1226</v>
       </c>
       <c r="C5" t="n">
-        <v>2667</v>
+        <v>3492</v>
       </c>
       <c r="D5" t="n">
-        <v>1543</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>598</v>
+        <v>749</v>
       </c>
       <c r="C6" t="n">
-        <v>1800</v>
+        <v>2284</v>
       </c>
       <c r="D6" t="n">
-        <v>831</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="C7" t="n">
-        <v>855</v>
+        <v>983</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>326</v>
+        <v>393</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4427</v>
+        <v>1876</v>
       </c>
       <c r="C2" t="n">
-        <v>11418</v>
+        <v>7272</v>
       </c>
       <c r="D2" t="n">
-        <v>26035</v>
+        <v>24464</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4083</v>
+        <v>2021</v>
       </c>
       <c r="C3" t="n">
-        <v>6547</v>
+        <v>9796</v>
       </c>
       <c r="D3" t="n">
-        <v>11339</v>
+        <v>13777</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2834</v>
+        <v>1132</v>
       </c>
       <c r="C4" t="n">
-        <v>5818</v>
+        <v>5616</v>
       </c>
       <c r="D4" t="n">
-        <v>5233</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1556</v>
+        <v>692</v>
       </c>
       <c r="C5" t="n">
-        <v>2870</v>
+        <v>2238</v>
       </c>
       <c r="D5" t="n">
-        <v>2016</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>819</v>
+        <v>256</v>
       </c>
       <c r="C6" t="n">
-        <v>2245</v>
+        <v>963</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>628</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>349</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>1354</v>
+        <v>385</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>592</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
         <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
